--- a/data/trans_dic/P36BPD01_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,37; 96,38</t>
+          <t>91,38; 96,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,38; 93,65</t>
+          <t>88,3; 93,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,81; 94,55</t>
+          <t>90,92; 94,58</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,25; 88,35</t>
+          <t>79,45; 88,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,21; 89,31</t>
+          <t>84,34; 89,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,85; 88,32</t>
+          <t>82,97; 88,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,62; 99,95</t>
+          <t>98,9; 99,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,49; 99,61</t>
+          <t>97,73; 99,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,46; 99,69</t>
+          <t>98,54; 99,68</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,42; 99,32</t>
+          <t>96,36; 99,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,36; 99,34</t>
+          <t>94,96; 99,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,4; 99,08</t>
+          <t>96,33; 99,07</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,88; 97,62</t>
+          <t>91,47; 97,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,18; 98,29</t>
+          <t>93,78; 98,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,22; 97,59</t>
+          <t>94,15; 97,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98,04; 99,88</t>
+          <t>98,08; 99,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,77; 99,24</t>
+          <t>95,44; 99,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,37; 99,37</t>
+          <t>97,44; 99,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,58; 98,4</t>
+          <t>95,55; 98,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,42; 99,03</t>
+          <t>96,44; 99,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,51</t>
+          <t>96,48; 98,5</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,12; 98,54</t>
+          <t>93,96; 98,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,43; 97,03</t>
+          <t>94,36; 97,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,89; 97,66</t>
+          <t>94,89; 97,61</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>94,22; 96,41</t>
+          <t>94,13; 96,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94,88; 96,43</t>
+          <t>94,85; 96,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94,8; 96,1</t>
+          <t>94,77; 96,15</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>284552; 300183</t>
+          <t>284602; 301254</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>255976; 271250</t>
+          <t>255738; 271495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>545817; 568310</t>
+          <t>546478; 568508</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>398391; 449808</t>
+          <t>404489; 451312</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>430657; 456719</t>
+          <t>431327; 457734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>845460; 901338</t>
+          <t>846698; 901583</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>309769; 313927</t>
+          <t>310647; 313927</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>339248; 346608</t>
+          <t>340086; 346627</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>651873; 660032</t>
+          <t>652366; 659963</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>301380; 310444</t>
+          <t>301169; 310209</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>453652; 472571</t>
+          <t>451738; 472351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>759925; 781010</t>
+          <t>759374; 780949</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>164224; 174492</t>
+          <t>163497; 174572</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>196159; 204720</t>
+          <t>195328; 204474</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>364640; 377673</t>
+          <t>364372; 377656</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>264351; 269302</t>
+          <t>264451; 269306</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>246188; 255104</t>
+          <t>245346; 254927</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>512848; 523388</t>
+          <t>513211; 523200</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>590129; 607525</t>
+          <t>589914; 607253</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>818861; 841051</t>
+          <t>819068; 841323</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1415023; 1444861</t>
+          <t>1415077; 1444677</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>874099; 915142</t>
+          <t>872622; 913217</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>676192; 694857</t>
+          <t>675747; 695346</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1560770; 1606324</t>
+          <t>1560854; 1605567</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3242677; 3318017</t>
+          <t>3239663; 3314832</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3468372; 3524900</t>
+          <t>3467078; 3528030</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6728011; 6820115</t>
+          <t>6725947; 6823898</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD01_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,38; 96,73</t>
+          <t>88,53; 94,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,3; 93,74</t>
+          <t>85,63; 91,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,92; 94,58</t>
+          <t>88,29; 92,5</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,45; 88,65</t>
+          <t>80,81; 89,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,34; 89,51</t>
+          <t>84,35; 89,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,97; 88,35</t>
+          <t>83,12; 88,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>98,9; 99,95</t>
+          <t>97,43; 99,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,73; 99,61</t>
+          <t>96,36; 99,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,54; 99,68</t>
+          <t>97,56; 99,35</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>96,36; 99,25</t>
+          <t>94,82; 98,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,96; 99,29</t>
+          <t>94,38; 98,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,33; 99,07</t>
+          <t>95,57; 98,59</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,47; 97,67</t>
+          <t>90,06; 96,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,78; 98,18</t>
+          <t>94,88; 97,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94,15; 97,58</t>
+          <t>92,88; 96,57</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98,08; 99,88</t>
+          <t>97,19; 99,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>95,44; 99,17</t>
+          <t>95,12; 98,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,44; 99,34</t>
+          <t>96,93; 99,04</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,55; 98,35</t>
+          <t>94,18; 97,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,44; 99,06</t>
+          <t>94,77; 97,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,5</t>
+          <t>95,18; 97,37</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>93,96; 98,33</t>
+          <t>90,15; 94,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>94,36; 97,1</t>
+          <t>93,16; 96,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,89; 97,61</t>
+          <t>92,28; 94,95</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>94,13; 96,31</t>
+          <t>92,76; 94,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>94,85; 96,52</t>
+          <t>93,79; 95,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94,77; 96,15</t>
+          <t>93,5; 94,74</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>293890</t>
+          <t>292561</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>265155</t>
+          <t>282302</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>559044</t>
+          <t>574863</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>284602; 301254</t>
+          <t>282266; 301257</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>255738; 271495</t>
+          <t>270634; 290231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>546478; 568508</t>
+          <t>560571; 587267</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>430157</t>
+          <t>444827</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>445534</t>
+          <t>472363</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>875691</t>
+          <t>917190</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>404489; 451312</t>
+          <t>421469; 464845</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>431327; 457734</t>
+          <t>456994; 484318</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>846698; 901583</t>
+          <t>883905; 939754</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>313052</t>
+          <t>311355</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>344289</t>
+          <t>349358</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>657342</t>
+          <t>660713</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>310647; 313927</t>
+          <t>306086; 313476</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>340086; 346627</t>
+          <t>342378; 352823</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>652366; 659963</t>
+          <t>653147; 665104</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>307337</t>
+          <t>363951</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>466938</t>
+          <t>412146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>774273</t>
+          <t>776098</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>301169; 310209</t>
+          <t>353814; 369153</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>451738; 472351</t>
+          <t>398234; 417687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>759374; 780949</t>
+          <t>759907; 783891</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>171234</t>
+          <t>192485</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>201615</t>
+          <t>219228</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372849</t>
+          <t>411713</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>163497; 174572</t>
+          <t>185226; 198225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>195328; 204474</t>
+          <t>215200; 222271</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>364372; 377656</t>
+          <t>401683; 417662</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>267689</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>251825</t>
+          <t>257588</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>519755</t>
+          <t>525277</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>264451; 269306</t>
+          <t>263088; 269825</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>245346; 254927</t>
+          <t>250882; 260844</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>513211; 523200</t>
+          <t>518040; 529328</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>600355</t>
+          <t>686726</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>831035</t>
+          <t>744160</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1431389</t>
+          <t>1430885</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>589914; 607253</t>
+          <t>671860; 697149</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>819068; 841323</t>
+          <t>731658; 753097</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1415077; 1444677</t>
+          <t>1413791; 1446376</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>892491</t>
+          <t>739023</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>687362</t>
+          <t>787035</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1579854</t>
+          <t>1526058</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>872622; 913217</t>
+          <t>719430; 752366</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>675747; 695346</t>
+          <t>772845; 798441</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1560854; 1605567</t>
+          <t>1501979; 1545401</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3239663; 3314832</t>
+          <t>3260980; 3328952</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3467078; 3528030</t>
+          <t>3495998; 3551130</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6725947; 6823898</t>
+          <t>6771769; 6861831</t>
         </is>
       </c>
     </row>
